--- a/assets/signaturepresets/lk-erz-2026.xlsx
+++ b/assets/signaturepresets/lk-erz-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\var\www\html\ruestzeit-anmeldung\assets\signaturepresets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1892872B-8873-493F-9325-13DB521E8137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34BBF711-5AA3-4966-B703-8551FFD2B286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="929" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30828" yWindow="-780" windowWidth="30936" windowHeight="16776" tabRatio="929" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VN - Anlage TN-Liste" sheetId="18" r:id="rId1"/>
@@ -546,9 +546,123 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -561,121 +675,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1055,101 +1055,101 @@
     <tabColor rgb="FF66CCFF"/>
   </sheetPr>
   <dimension ref="A1:S89"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.88671875" style="5" customWidth="1"/>
-    <col min="3" max="3" width="8.109375" style="5" customWidth="1"/>
-    <col min="4" max="4" width="9.33203125" style="5" customWidth="1"/>
-    <col min="5" max="5" width="11.109375" style="5" customWidth="1"/>
-    <col min="6" max="6" width="11.21875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="8.140625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="9.28515625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="11.140625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" style="5" customWidth="1"/>
     <col min="7" max="7" width="7" style="1" customWidth="1"/>
-    <col min="8" max="8" width="18.6640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="6.77734375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="7.44140625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="29.77734375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.7109375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.42578125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="29.7109375" style="1" customWidth="1"/>
     <col min="12" max="19" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="4" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A1" s="55" t="s">
+    <row r="1" spans="1:19" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+      <c r="A1" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="56" t="s">
+      <c r="B1" s="76"/>
+      <c r="C1" s="77" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-    </row>
-    <row r="2" spans="1:19" s="4" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+    </row>
+    <row r="2" spans="1:19" s="4" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="8"/>
-      <c r="B2" s="75"/>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
       <c r="J2" s="8"/>
       <c r="K2" s="8"/>
     </row>
-    <row r="3" spans="1:19" s="4" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" s="4" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="87" t="s">
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
       <c r="G3" s="10"/>
       <c r="H3" s="11"/>
       <c r="I3" s="10"/>
       <c r="J3" s="10"/>
       <c r="K3" s="10"/>
     </row>
-    <row r="4" spans="1:19" s="4" customFormat="1" ht="31.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="62"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="61"/>
+    <row r="4" spans="1:19" s="4" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="83"/>
+      <c r="B4" s="84"/>
+      <c r="C4" s="84"/>
+      <c r="D4" s="81"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="82"/>
       <c r="H4" s="12"/>
       <c r="I4" s="9"/>
       <c r="J4" s="9"/>
       <c r="K4" s="9"/>
     </row>
-    <row r="5" spans="1:19" s="4" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="62"/>
-      <c r="B5" s="63"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="88" t="s">
+    <row r="5" spans="1:19" s="4" customFormat="1" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="83"/>
+      <c r="B5" s="84"/>
+      <c r="C5" s="84"/>
+      <c r="D5" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="89"/>
-      <c r="F5" s="90"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="63"/>
       <c r="G5" s="8"/>
       <c r="H5" s="12"/>
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
       <c r="K5" s="9"/>
     </row>
-    <row r="6" spans="1:19" s="4" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="64"/>
-      <c r="B6" s="65"/>
-      <c r="C6" s="65"/>
+    <row r="6" spans="1:19" s="4" customFormat="1" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="85"/>
+      <c r="B6" s="86"/>
+      <c r="C6" s="86"/>
       <c r="D6" s="42" t="s">
         <v>11</v>
       </c>
@@ -1159,47 +1159,47 @@
       <c r="F6" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="52" t="s">
+      <c r="G6" s="90" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="53"/>
-    </row>
-    <row r="7" spans="1:19" s="33" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="H6" s="91"/>
+    </row>
+    <row r="7" spans="1:19" s="33" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A7" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="68" t="s">
+      <c r="B7" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="69"/>
-      <c r="D7" s="71" t="s">
+      <c r="C7" s="70"/>
+      <c r="D7" s="72" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="72"/>
-      <c r="F7" s="73"/>
+      <c r="E7" s="73"/>
+      <c r="F7" s="74"/>
       <c r="G7" s="38" t="s">
         <v>2</v>
       </c>
       <c r="H7" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="I7" s="68" t="s">
+      <c r="I7" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="J7" s="70"/>
-      <c r="K7" s="66" t="s">
+      <c r="J7" s="71"/>
+      <c r="K7" s="87" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
-      <c r="B8" s="77"/>
-      <c r="C8" s="78"/>
-      <c r="D8" s="57" t="s">
+      <c r="B8" s="52"/>
+      <c r="C8" s="53"/>
+      <c r="D8" s="78" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="58"/>
-      <c r="F8" s="59"/>
+      <c r="E8" s="79"/>
+      <c r="F8" s="80"/>
       <c r="G8" s="15"/>
       <c r="H8" s="15"/>
       <c r="I8" s="26" t="s">
@@ -1208,17 +1208,17 @@
       <c r="J8" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="K8" s="67"/>
-    </row>
-    <row r="9" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K8" s="88"/>
+    </row>
+    <row r="9" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>1</v>
       </c>
-      <c r="B9" s="79"/>
-      <c r="C9" s="80"/>
-      <c r="D9" s="79"/>
-      <c r="E9" s="91"/>
-      <c r="F9" s="80"/>
+      <c r="B9" s="67"/>
+      <c r="C9" s="68"/>
+      <c r="D9" s="67"/>
+      <c r="E9" s="93"/>
+      <c r="F9" s="68"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
       <c r="I9" s="7"/>
@@ -1233,15 +1233,15 @@
       <c r="R9" s="4"/>
       <c r="S9" s="21"/>
     </row>
-    <row r="10" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>2</v>
       </c>
-      <c r="B10" s="79"/>
-      <c r="C10" s="80"/>
-      <c r="D10" s="79"/>
-      <c r="E10" s="91"/>
-      <c r="F10" s="80"/>
+      <c r="B10" s="67"/>
+      <c r="C10" s="68"/>
+      <c r="D10" s="67"/>
+      <c r="E10" s="93"/>
+      <c r="F10" s="68"/>
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
       <c r="I10" s="7"/>
@@ -1256,15 +1256,15 @@
       <c r="R10" s="4"/>
       <c r="S10" s="21"/>
     </row>
-    <row r="11" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>3</v>
       </c>
-      <c r="B11" s="79"/>
-      <c r="C11" s="80"/>
-      <c r="D11" s="79"/>
-      <c r="E11" s="91"/>
-      <c r="F11" s="80"/>
+      <c r="B11" s="67"/>
+      <c r="C11" s="68"/>
+      <c r="D11" s="67"/>
+      <c r="E11" s="93"/>
+      <c r="F11" s="68"/>
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>
       <c r="I11" s="7"/>
@@ -1279,15 +1279,15 @@
       <c r="R11" s="4"/>
       <c r="S11" s="21"/>
     </row>
-    <row r="12" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>4</v>
       </c>
-      <c r="B12" s="79"/>
-      <c r="C12" s="80"/>
-      <c r="D12" s="79"/>
-      <c r="E12" s="91"/>
-      <c r="F12" s="80"/>
+      <c r="B12" s="67"/>
+      <c r="C12" s="68"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="93"/>
+      <c r="F12" s="68"/>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
@@ -1302,15 +1302,15 @@
       <c r="R12" s="4"/>
       <c r="S12" s="21"/>
     </row>
-    <row r="13" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>5</v>
       </c>
-      <c r="B13" s="79"/>
-      <c r="C13" s="80"/>
-      <c r="D13" s="79"/>
-      <c r="E13" s="91"/>
-      <c r="F13" s="80"/>
+      <c r="B13" s="67"/>
+      <c r="C13" s="68"/>
+      <c r="D13" s="67"/>
+      <c r="E13" s="93"/>
+      <c r="F13" s="68"/>
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
       <c r="I13" s="7"/>
@@ -1325,15 +1325,15 @@
       <c r="R13" s="4"/>
       <c r="S13" s="21"/>
     </row>
-    <row r="14" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>6</v>
       </c>
-      <c r="B14" s="79"/>
-      <c r="C14" s="80"/>
-      <c r="D14" s="79"/>
-      <c r="E14" s="91"/>
-      <c r="F14" s="80"/>
+      <c r="B14" s="67"/>
+      <c r="C14" s="68"/>
+      <c r="D14" s="67"/>
+      <c r="E14" s="93"/>
+      <c r="F14" s="68"/>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
       <c r="I14" s="7"/>
@@ -1348,15 +1348,15 @@
       <c r="R14" s="4"/>
       <c r="S14" s="21"/>
     </row>
-    <row r="15" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>7</v>
       </c>
-      <c r="B15" s="79"/>
-      <c r="C15" s="80"/>
-      <c r="D15" s="79"/>
-      <c r="E15" s="91"/>
-      <c r="F15" s="80"/>
+      <c r="B15" s="67"/>
+      <c r="C15" s="68"/>
+      <c r="D15" s="67"/>
+      <c r="E15" s="93"/>
+      <c r="F15" s="68"/>
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
@@ -1371,15 +1371,15 @@
       <c r="R15" s="4"/>
       <c r="S15" s="21"/>
     </row>
-    <row r="16" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>8</v>
       </c>
-      <c r="B16" s="81"/>
-      <c r="C16" s="82"/>
-      <c r="D16" s="81"/>
-      <c r="E16" s="92"/>
-      <c r="F16" s="82"/>
+      <c r="B16" s="54"/>
+      <c r="C16" s="55"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="64"/>
+      <c r="F16" s="55"/>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
@@ -1394,15 +1394,15 @@
       <c r="R16" s="4"/>
       <c r="S16" s="21"/>
     </row>
-    <row r="17" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>9</v>
       </c>
-      <c r="B17" s="81"/>
-      <c r="C17" s="82"/>
-      <c r="D17" s="81"/>
-      <c r="E17" s="92"/>
-      <c r="F17" s="82"/>
+      <c r="B17" s="54"/>
+      <c r="C17" s="55"/>
+      <c r="D17" s="54"/>
+      <c r="E17" s="64"/>
+      <c r="F17" s="55"/>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
       <c r="I17" s="7"/>
@@ -1417,15 +1417,15 @@
       <c r="R17" s="4"/>
       <c r="S17" s="21"/>
     </row>
-    <row r="18" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>10</v>
       </c>
-      <c r="B18" s="81"/>
-      <c r="C18" s="82"/>
-      <c r="D18" s="81"/>
-      <c r="E18" s="92"/>
-      <c r="F18" s="82"/>
+      <c r="B18" s="54"/>
+      <c r="C18" s="55"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="64"/>
+      <c r="F18" s="55"/>
       <c r="G18" s="7"/>
       <c r="H18" s="7"/>
       <c r="I18" s="7"/>
@@ -1440,15 +1440,15 @@
       <c r="R18" s="4"/>
       <c r="S18" s="21"/>
     </row>
-    <row r="19" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>11</v>
       </c>
-      <c r="B19" s="81"/>
-      <c r="C19" s="82"/>
-      <c r="D19" s="81"/>
-      <c r="E19" s="92"/>
-      <c r="F19" s="82"/>
+      <c r="B19" s="54"/>
+      <c r="C19" s="55"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="64"/>
+      <c r="F19" s="55"/>
       <c r="G19" s="7"/>
       <c r="H19" s="7"/>
       <c r="I19" s="7"/>
@@ -1463,15 +1463,15 @@
       <c r="R19" s="4"/>
       <c r="S19" s="21"/>
     </row>
-    <row r="20" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>12</v>
       </c>
-      <c r="B20" s="81"/>
-      <c r="C20" s="82"/>
-      <c r="D20" s="81"/>
-      <c r="E20" s="92"/>
-      <c r="F20" s="82"/>
+      <c r="B20" s="54"/>
+      <c r="C20" s="55"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="64"/>
+      <c r="F20" s="55"/>
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
@@ -1486,15 +1486,15 @@
       <c r="R20" s="4"/>
       <c r="S20" s="21"/>
     </row>
-    <row r="21" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>13</v>
       </c>
-      <c r="B21" s="81"/>
-      <c r="C21" s="82"/>
-      <c r="D21" s="81"/>
-      <c r="E21" s="92"/>
-      <c r="F21" s="82"/>
+      <c r="B21" s="54"/>
+      <c r="C21" s="55"/>
+      <c r="D21" s="54"/>
+      <c r="E21" s="64"/>
+      <c r="F21" s="55"/>
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
@@ -1509,7 +1509,7 @@
       <c r="R21" s="4"/>
       <c r="S21" s="21"/>
     </row>
-    <row r="22" spans="1:19" s="16" customFormat="1" ht="7.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" s="16" customFormat="1" ht="7.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="17"/>
       <c r="B22" s="18"/>
       <c r="C22" s="18"/>
@@ -1530,12 +1530,12 @@
       <c r="R22" s="4"/>
       <c r="S22" s="21"/>
     </row>
-    <row r="23" spans="1:19" s="19" customFormat="1" ht="3.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" s="19" customFormat="1" ht="3.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B23" s="37"/>
-      <c r="C23" s="83"/>
-      <c r="D23" s="83"/>
-      <c r="E23" s="83"/>
-      <c r="F23" s="83"/>
+      <c r="C23" s="56"/>
+      <c r="D23" s="56"/>
+      <c r="E23" s="56"/>
+      <c r="F23" s="56"/>
       <c r="G23" s="35"/>
       <c r="H23" s="35"/>
       <c r="I23" s="35"/>
@@ -1550,36 +1550,36 @@
       <c r="R23" s="23"/>
       <c r="S23" s="22"/>
     </row>
-    <row r="24" spans="1:19" s="23" customFormat="1" ht="70.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" s="23" customFormat="1" ht="70.150000000000006" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="36"/>
-      <c r="B24" s="54" t="s">
+      <c r="B24" s="92" t="s">
         <v>17</v>
       </c>
-      <c r="C24" s="54"/>
-      <c r="D24" s="54"/>
+      <c r="C24" s="92"/>
+      <c r="D24" s="92"/>
       <c r="E24" s="39"/>
-      <c r="F24" s="90"/>
+      <c r="F24" s="63"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
     </row>
-    <row r="25" spans="1:19" s="45" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="51" t="s">
+    <row r="25" spans="1:19" s="45" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="89" t="s">
         <v>18</v>
       </c>
-      <c r="C25" s="51"/>
-      <c r="D25" s="51"/>
+      <c r="C25" s="89"/>
+      <c r="D25" s="89"/>
       <c r="E25" s="46"/>
-      <c r="F25" s="93"/>
+      <c r="F25" s="65"/>
       <c r="G25" s="47"/>
       <c r="H25" s="47"/>
       <c r="I25" s="47"/>
       <c r="J25" s="47"/>
       <c r="K25" s="47"/>
     </row>
-    <row r="26" spans="1:19" s="33" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" s="33" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A26" s="29" t="s">
         <v>0</v>
       </c>
@@ -1606,10 +1606,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="15"/>
-      <c r="B27" s="77"/>
-      <c r="C27" s="78"/>
+      <c r="B27" s="52"/>
+      <c r="C27" s="53"/>
       <c r="D27" s="24" t="s">
         <v>16</v>
       </c>
@@ -1625,14 +1625,14 @@
       </c>
       <c r="K27" s="28"/>
     </row>
-    <row r="28" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
         <v>14</v>
       </c>
-      <c r="B28" s="84"/>
-      <c r="C28" s="85"/>
-      <c r="D28" s="86"/>
-      <c r="E28" s="86"/>
+      <c r="B28" s="57"/>
+      <c r="C28" s="58"/>
+      <c r="D28" s="59"/>
+      <c r="E28" s="59"/>
       <c r="F28" s="18"/>
       <c r="G28" s="7"/>
       <c r="H28" s="7"/>
@@ -1648,15 +1648,15 @@
       <c r="R28" s="4"/>
       <c r="S28" s="21"/>
     </row>
-    <row r="29" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
         <v>15</v>
       </c>
-      <c r="B29" s="84"/>
-      <c r="C29" s="85"/>
-      <c r="D29" s="86"/>
-      <c r="E29" s="86"/>
-      <c r="F29" s="86"/>
+      <c r="B29" s="57"/>
+      <c r="C29" s="58"/>
+      <c r="D29" s="59"/>
+      <c r="E29" s="59"/>
+      <c r="F29" s="59"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
@@ -1671,15 +1671,15 @@
       <c r="R29" s="4"/>
       <c r="S29" s="21"/>
     </row>
-    <row r="30" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
         <v>16</v>
       </c>
-      <c r="B30" s="84"/>
-      <c r="C30" s="85"/>
-      <c r="D30" s="86"/>
-      <c r="E30" s="86"/>
-      <c r="F30" s="86"/>
+      <c r="B30" s="57"/>
+      <c r="C30" s="58"/>
+      <c r="D30" s="59"/>
+      <c r="E30" s="59"/>
+      <c r="F30" s="59"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
@@ -1694,15 +1694,15 @@
       <c r="R30" s="4"/>
       <c r="S30" s="21"/>
     </row>
-    <row r="31" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
         <v>17</v>
       </c>
-      <c r="B31" s="84"/>
-      <c r="C31" s="85"/>
-      <c r="D31" s="86"/>
-      <c r="E31" s="86"/>
-      <c r="F31" s="86"/>
+      <c r="B31" s="57"/>
+      <c r="C31" s="58"/>
+      <c r="D31" s="59"/>
+      <c r="E31" s="59"/>
+      <c r="F31" s="59"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
@@ -1717,15 +1717,15 @@
       <c r="R31" s="4"/>
       <c r="S31" s="21"/>
     </row>
-    <row r="32" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="3">
         <v>18</v>
       </c>
-      <c r="B32" s="84"/>
-      <c r="C32" s="85"/>
-      <c r="D32" s="86"/>
-      <c r="E32" s="86"/>
-      <c r="F32" s="86"/>
+      <c r="B32" s="57"/>
+      <c r="C32" s="58"/>
+      <c r="D32" s="59"/>
+      <c r="E32" s="59"/>
+      <c r="F32" s="59"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
@@ -1740,15 +1740,15 @@
       <c r="R32" s="4"/>
       <c r="S32" s="21"/>
     </row>
-    <row r="33" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="3">
         <v>19</v>
       </c>
-      <c r="B33" s="84"/>
-      <c r="C33" s="85"/>
-      <c r="D33" s="86"/>
-      <c r="E33" s="86"/>
-      <c r="F33" s="86"/>
+      <c r="B33" s="57"/>
+      <c r="C33" s="58"/>
+      <c r="D33" s="59"/>
+      <c r="E33" s="59"/>
+      <c r="F33" s="59"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
@@ -1763,15 +1763,15 @@
       <c r="R33" s="4"/>
       <c r="S33" s="21"/>
     </row>
-    <row r="34" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="3">
         <v>20</v>
       </c>
-      <c r="B34" s="84"/>
-      <c r="C34" s="85"/>
-      <c r="D34" s="86"/>
-      <c r="E34" s="86"/>
-      <c r="F34" s="86"/>
+      <c r="B34" s="57"/>
+      <c r="C34" s="58"/>
+      <c r="D34" s="59"/>
+      <c r="E34" s="59"/>
+      <c r="F34" s="59"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
@@ -1786,15 +1786,15 @@
       <c r="R34" s="4"/>
       <c r="S34" s="21"/>
     </row>
-    <row r="35" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="3">
         <v>21</v>
       </c>
-      <c r="B35" s="86"/>
-      <c r="C35" s="86"/>
-      <c r="D35" s="86"/>
-      <c r="E35" s="86"/>
-      <c r="F35" s="86"/>
+      <c r="B35" s="59"/>
+      <c r="C35" s="59"/>
+      <c r="D35" s="59"/>
+      <c r="E35" s="59"/>
+      <c r="F35" s="59"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
@@ -1809,15 +1809,15 @@
       <c r="R35" s="4"/>
       <c r="S35" s="21"/>
     </row>
-    <row r="36" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="3">
         <v>22</v>
       </c>
-      <c r="B36" s="86"/>
-      <c r="C36" s="86"/>
-      <c r="D36" s="86"/>
-      <c r="E36" s="86"/>
-      <c r="F36" s="86"/>
+      <c r="B36" s="59"/>
+      <c r="C36" s="59"/>
+      <c r="D36" s="59"/>
+      <c r="E36" s="59"/>
+      <c r="F36" s="59"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
@@ -1832,15 +1832,15 @@
       <c r="R36" s="4"/>
       <c r="S36" s="21"/>
     </row>
-    <row r="37" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="3">
         <v>23</v>
       </c>
-      <c r="B37" s="86"/>
-      <c r="C37" s="86"/>
-      <c r="D37" s="86"/>
-      <c r="E37" s="86"/>
-      <c r="F37" s="86"/>
+      <c r="B37" s="59"/>
+      <c r="C37" s="59"/>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
@@ -1855,15 +1855,15 @@
       <c r="R37" s="4"/>
       <c r="S37" s="21"/>
     </row>
-    <row r="38" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="3">
         <v>24</v>
       </c>
-      <c r="B38" s="86"/>
-      <c r="C38" s="86"/>
-      <c r="D38" s="86"/>
-      <c r="E38" s="86"/>
-      <c r="F38" s="86"/>
+      <c r="B38" s="59"/>
+      <c r="C38" s="59"/>
+      <c r="D38" s="59"/>
+      <c r="E38" s="59"/>
+      <c r="F38" s="59"/>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
@@ -1878,15 +1878,15 @@
       <c r="R38" s="4"/>
       <c r="S38" s="21"/>
     </row>
-    <row r="39" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="3">
         <v>25</v>
       </c>
-      <c r="B39" s="86"/>
-      <c r="C39" s="86"/>
-      <c r="D39" s="86"/>
-      <c r="E39" s="86"/>
-      <c r="F39" s="86"/>
+      <c r="B39" s="59"/>
+      <c r="C39" s="59"/>
+      <c r="D39" s="59"/>
+      <c r="E39" s="59"/>
+      <c r="F39" s="59"/>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
@@ -1901,15 +1901,15 @@
       <c r="R39" s="4"/>
       <c r="S39" s="21"/>
     </row>
-    <row r="40" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="3">
         <v>26</v>
       </c>
-      <c r="B40" s="86"/>
-      <c r="C40" s="86"/>
-      <c r="D40" s="86"/>
-      <c r="E40" s="86"/>
-      <c r="F40" s="86"/>
+      <c r="B40" s="59"/>
+      <c r="C40" s="59"/>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
@@ -1924,15 +1924,15 @@
       <c r="R40" s="4"/>
       <c r="S40" s="21"/>
     </row>
-    <row r="41" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="3">
         <v>27</v>
       </c>
-      <c r="B41" s="86"/>
-      <c r="C41" s="86"/>
-      <c r="D41" s="86"/>
-      <c r="E41" s="86"/>
-      <c r="F41" s="86"/>
+      <c r="B41" s="59"/>
+      <c r="C41" s="59"/>
+      <c r="D41" s="59"/>
+      <c r="E41" s="59"/>
+      <c r="F41" s="59"/>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
       <c r="I41" s="2"/>
@@ -1947,15 +1947,15 @@
       <c r="R41" s="4"/>
       <c r="S41" s="21"/>
     </row>
-    <row r="42" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="3">
         <v>28</v>
       </c>
-      <c r="B42" s="86"/>
-      <c r="C42" s="86"/>
-      <c r="D42" s="86"/>
-      <c r="E42" s="86"/>
-      <c r="F42" s="86"/>
+      <c r="B42" s="59"/>
+      <c r="C42" s="59"/>
+      <c r="D42" s="59"/>
+      <c r="E42" s="59"/>
+      <c r="F42" s="59"/>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
@@ -1970,15 +1970,15 @@
       <c r="R42" s="4"/>
       <c r="S42" s="21"/>
     </row>
-    <row r="43" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="3">
         <v>29</v>
       </c>
-      <c r="B43" s="86"/>
-      <c r="C43" s="86"/>
-      <c r="D43" s="86"/>
-      <c r="E43" s="86"/>
-      <c r="F43" s="86"/>
+      <c r="B43" s="59"/>
+      <c r="C43" s="59"/>
+      <c r="D43" s="59"/>
+      <c r="E43" s="59"/>
+      <c r="F43" s="59"/>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
@@ -1993,15 +1993,15 @@
       <c r="R43" s="4"/>
       <c r="S43" s="21"/>
     </row>
-    <row r="44" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="3">
         <v>30</v>
       </c>
-      <c r="B44" s="86"/>
-      <c r="C44" s="86"/>
-      <c r="D44" s="86"/>
-      <c r="E44" s="86"/>
-      <c r="F44" s="86"/>
+      <c r="B44" s="59"/>
+      <c r="C44" s="59"/>
+      <c r="D44" s="59"/>
+      <c r="E44" s="59"/>
+      <c r="F44" s="59"/>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
@@ -2016,36 +2016,36 @@
       <c r="R44" s="4"/>
       <c r="S44" s="21"/>
     </row>
-    <row r="45" spans="1:19" s="23" customFormat="1" ht="70.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:19" s="23" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="36"/>
-      <c r="B45" s="50" t="s">
+      <c r="B45" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="C45" s="50"/>
-      <c r="D45" s="50"/>
+      <c r="C45" s="75"/>
+      <c r="D45" s="75"/>
       <c r="E45" s="39"/>
-      <c r="F45" s="90"/>
+      <c r="F45" s="63"/>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
       <c r="I45" s="4"/>
       <c r="J45" s="4"/>
       <c r="K45" s="4"/>
     </row>
-    <row r="46" spans="1:19" s="45" customFormat="1" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="74" t="s">
+    <row r="46" spans="1:19" s="45" customFormat="1" ht="24.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B46" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="C46" s="74"/>
-      <c r="D46" s="74"/>
+      <c r="C46" s="66"/>
+      <c r="D46" s="66"/>
       <c r="E46" s="46"/>
-      <c r="F46" s="93"/>
+      <c r="F46" s="65"/>
       <c r="G46" s="47"/>
       <c r="H46" s="47"/>
       <c r="I46" s="47"/>
       <c r="J46" s="47"/>
       <c r="K46" s="47"/>
     </row>
-    <row r="47" spans="1:19" s="33" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19" s="33" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A47" s="29" t="s">
         <v>0</v>
       </c>
@@ -2072,10 +2072,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A48" s="15"/>
-      <c r="B48" s="77"/>
-      <c r="C48" s="78"/>
+      <c r="B48" s="52"/>
+      <c r="C48" s="53"/>
       <c r="D48" s="24" t="s">
         <v>16</v>
       </c>
@@ -2091,14 +2091,14 @@
       </c>
       <c r="K48" s="28"/>
     </row>
-    <row r="49" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="3">
         <v>31</v>
       </c>
-      <c r="B49" s="84"/>
-      <c r="C49" s="85"/>
-      <c r="D49" s="86"/>
-      <c r="E49" s="86"/>
+      <c r="B49" s="57"/>
+      <c r="C49" s="58"/>
+      <c r="D49" s="59"/>
+      <c r="E49" s="59"/>
       <c r="F49" s="18"/>
       <c r="G49" s="7"/>
       <c r="H49" s="7"/>
@@ -2114,15 +2114,15 @@
       <c r="R49" s="4"/>
       <c r="S49" s="21"/>
     </row>
-    <row r="50" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="3">
         <v>32</v>
       </c>
-      <c r="B50" s="84"/>
-      <c r="C50" s="85"/>
-      <c r="D50" s="86"/>
-      <c r="E50" s="86"/>
-      <c r="F50" s="86"/>
+      <c r="B50" s="57"/>
+      <c r="C50" s="58"/>
+      <c r="D50" s="59"/>
+      <c r="E50" s="59"/>
+      <c r="F50" s="59"/>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
@@ -2137,15 +2137,15 @@
       <c r="R50" s="4"/>
       <c r="S50" s="21"/>
     </row>
-    <row r="51" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="3">
         <v>33</v>
       </c>
-      <c r="B51" s="84"/>
-      <c r="C51" s="85"/>
-      <c r="D51" s="86"/>
-      <c r="E51" s="86"/>
-      <c r="F51" s="86"/>
+      <c r="B51" s="57"/>
+      <c r="C51" s="58"/>
+      <c r="D51" s="59"/>
+      <c r="E51" s="59"/>
+      <c r="F51" s="59"/>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
@@ -2160,15 +2160,15 @@
       <c r="R51" s="4"/>
       <c r="S51" s="21"/>
     </row>
-    <row r="52" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="3">
         <v>34</v>
       </c>
-      <c r="B52" s="84"/>
-      <c r="C52" s="85"/>
-      <c r="D52" s="86"/>
-      <c r="E52" s="86"/>
-      <c r="F52" s="86"/>
+      <c r="B52" s="57"/>
+      <c r="C52" s="58"/>
+      <c r="D52" s="59"/>
+      <c r="E52" s="59"/>
+      <c r="F52" s="59"/>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
       <c r="I52" s="2"/>
@@ -2183,15 +2183,15 @@
       <c r="R52" s="4"/>
       <c r="S52" s="21"/>
     </row>
-    <row r="53" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="3">
         <v>35</v>
       </c>
-      <c r="B53" s="84"/>
-      <c r="C53" s="85"/>
-      <c r="D53" s="86"/>
-      <c r="E53" s="86"/>
-      <c r="F53" s="86"/>
+      <c r="B53" s="57"/>
+      <c r="C53" s="58"/>
+      <c r="D53" s="59"/>
+      <c r="E53" s="59"/>
+      <c r="F53" s="59"/>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
       <c r="I53" s="2"/>
@@ -2206,15 +2206,15 @@
       <c r="R53" s="4"/>
       <c r="S53" s="21"/>
     </row>
-    <row r="54" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="3">
         <v>36</v>
       </c>
-      <c r="B54" s="84"/>
-      <c r="C54" s="85"/>
-      <c r="D54" s="86"/>
-      <c r="E54" s="86"/>
-      <c r="F54" s="86"/>
+      <c r="B54" s="57"/>
+      <c r="C54" s="58"/>
+      <c r="D54" s="59"/>
+      <c r="E54" s="59"/>
+      <c r="F54" s="59"/>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
       <c r="I54" s="2"/>
@@ -2229,15 +2229,15 @@
       <c r="R54" s="4"/>
       <c r="S54" s="21"/>
     </row>
-    <row r="55" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="3">
         <v>37</v>
       </c>
-      <c r="B55" s="84"/>
-      <c r="C55" s="85"/>
-      <c r="D55" s="86"/>
-      <c r="E55" s="86"/>
-      <c r="F55" s="86"/>
+      <c r="B55" s="57"/>
+      <c r="C55" s="58"/>
+      <c r="D55" s="59"/>
+      <c r="E55" s="59"/>
+      <c r="F55" s="59"/>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
       <c r="I55" s="2"/>
@@ -2252,15 +2252,15 @@
       <c r="R55" s="4"/>
       <c r="S55" s="21"/>
     </row>
-    <row r="56" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="3">
         <v>38</v>
       </c>
-      <c r="B56" s="86"/>
-      <c r="C56" s="86"/>
-      <c r="D56" s="86"/>
-      <c r="E56" s="86"/>
-      <c r="F56" s="86"/>
+      <c r="B56" s="59"/>
+      <c r="C56" s="59"/>
+      <c r="D56" s="59"/>
+      <c r="E56" s="59"/>
+      <c r="F56" s="59"/>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
       <c r="I56" s="2"/>
@@ -2275,15 +2275,15 @@
       <c r="R56" s="4"/>
       <c r="S56" s="21"/>
     </row>
-    <row r="57" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="3">
         <v>39</v>
       </c>
-      <c r="B57" s="86"/>
-      <c r="C57" s="86"/>
-      <c r="D57" s="86"/>
-      <c r="E57" s="86"/>
-      <c r="F57" s="86"/>
+      <c r="B57" s="59"/>
+      <c r="C57" s="59"/>
+      <c r="D57" s="59"/>
+      <c r="E57" s="59"/>
+      <c r="F57" s="59"/>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
       <c r="I57" s="2"/>
@@ -2298,15 +2298,15 @@
       <c r="R57" s="4"/>
       <c r="S57" s="21"/>
     </row>
-    <row r="58" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="3">
         <v>40</v>
       </c>
-      <c r="B58" s="86"/>
-      <c r="C58" s="86"/>
-      <c r="D58" s="86"/>
-      <c r="E58" s="86"/>
-      <c r="F58" s="86"/>
+      <c r="B58" s="59"/>
+      <c r="C58" s="59"/>
+      <c r="D58" s="59"/>
+      <c r="E58" s="59"/>
+      <c r="F58" s="59"/>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
       <c r="I58" s="2"/>
@@ -2321,15 +2321,15 @@
       <c r="R58" s="4"/>
       <c r="S58" s="21"/>
     </row>
-    <row r="59" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="3">
         <v>41</v>
       </c>
-      <c r="B59" s="86"/>
-      <c r="C59" s="86"/>
-      <c r="D59" s="86"/>
-      <c r="E59" s="86"/>
-      <c r="F59" s="86"/>
+      <c r="B59" s="59"/>
+      <c r="C59" s="59"/>
+      <c r="D59" s="59"/>
+      <c r="E59" s="59"/>
+      <c r="F59" s="59"/>
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
       <c r="I59" s="2"/>
@@ -2344,15 +2344,15 @@
       <c r="R59" s="4"/>
       <c r="S59" s="21"/>
     </row>
-    <row r="60" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="3">
         <v>42</v>
       </c>
-      <c r="B60" s="86"/>
-      <c r="C60" s="86"/>
-      <c r="D60" s="86"/>
-      <c r="E60" s="86"/>
-      <c r="F60" s="86"/>
+      <c r="B60" s="59"/>
+      <c r="C60" s="59"/>
+      <c r="D60" s="59"/>
+      <c r="E60" s="59"/>
+      <c r="F60" s="59"/>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
       <c r="I60" s="2"/>
@@ -2367,15 +2367,15 @@
       <c r="R60" s="4"/>
       <c r="S60" s="21"/>
     </row>
-    <row r="61" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="3">
         <v>43</v>
       </c>
-      <c r="B61" s="86"/>
-      <c r="C61" s="86"/>
-      <c r="D61" s="86"/>
-      <c r="E61" s="86"/>
-      <c r="F61" s="86"/>
+      <c r="B61" s="59"/>
+      <c r="C61" s="59"/>
+      <c r="D61" s="59"/>
+      <c r="E61" s="59"/>
+      <c r="F61" s="59"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
@@ -2390,15 +2390,15 @@
       <c r="R61" s="4"/>
       <c r="S61" s="21"/>
     </row>
-    <row r="62" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="3">
         <v>44</v>
       </c>
-      <c r="B62" s="86"/>
-      <c r="C62" s="86"/>
-      <c r="D62" s="86"/>
-      <c r="E62" s="86"/>
-      <c r="F62" s="86"/>
+      <c r="B62" s="59"/>
+      <c r="C62" s="59"/>
+      <c r="D62" s="59"/>
+      <c r="E62" s="59"/>
+      <c r="F62" s="59"/>
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
       <c r="I62" s="2"/>
@@ -2413,15 +2413,15 @@
       <c r="R62" s="4"/>
       <c r="S62" s="21"/>
     </row>
-    <row r="63" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="3">
         <v>45</v>
       </c>
-      <c r="B63" s="86"/>
-      <c r="C63" s="86"/>
-      <c r="D63" s="86"/>
-      <c r="E63" s="86"/>
-      <c r="F63" s="86"/>
+      <c r="B63" s="59"/>
+      <c r="C63" s="59"/>
+      <c r="D63" s="59"/>
+      <c r="E63" s="59"/>
+      <c r="F63" s="59"/>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
@@ -2436,15 +2436,15 @@
       <c r="R63" s="4"/>
       <c r="S63" s="21"/>
     </row>
-    <row r="64" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="3">
         <v>46</v>
       </c>
-      <c r="B64" s="86"/>
-      <c r="C64" s="86"/>
-      <c r="D64" s="86"/>
-      <c r="E64" s="86"/>
-      <c r="F64" s="86"/>
+      <c r="B64" s="59"/>
+      <c r="C64" s="59"/>
+      <c r="D64" s="59"/>
+      <c r="E64" s="59"/>
+      <c r="F64" s="59"/>
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
       <c r="I64" s="2"/>
@@ -2459,15 +2459,15 @@
       <c r="R64" s="4"/>
       <c r="S64" s="21"/>
     </row>
-    <row r="65" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="3">
         <v>47</v>
       </c>
-      <c r="B65" s="86"/>
-      <c r="C65" s="86"/>
-      <c r="D65" s="86"/>
-      <c r="E65" s="86"/>
-      <c r="F65" s="86"/>
+      <c r="B65" s="59"/>
+      <c r="C65" s="59"/>
+      <c r="D65" s="59"/>
+      <c r="E65" s="59"/>
+      <c r="F65" s="59"/>
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
       <c r="I65" s="2"/>
@@ -2482,36 +2482,36 @@
       <c r="R65" s="4"/>
       <c r="S65" s="21"/>
     </row>
-    <row r="66" spans="1:19" s="23" customFormat="1" ht="70.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" s="23" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="36"/>
-      <c r="B66" s="50" t="s">
+      <c r="B66" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="C66" s="50"/>
-      <c r="D66" s="50"/>
+      <c r="C66" s="75"/>
+      <c r="D66" s="75"/>
       <c r="E66" s="39"/>
-      <c r="F66" s="90"/>
+      <c r="F66" s="63"/>
       <c r="G66" s="4"/>
       <c r="H66" s="4"/>
       <c r="I66" s="4"/>
       <c r="J66" s="4"/>
       <c r="K66" s="4"/>
     </row>
-    <row r="67" spans="1:19" s="45" customFormat="1" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="51" t="s">
+    <row r="67" spans="1:19" s="45" customFormat="1" ht="24.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B67" s="89" t="s">
         <v>18</v>
       </c>
-      <c r="C67" s="51"/>
-      <c r="D67" s="51"/>
+      <c r="C67" s="89"/>
+      <c r="D67" s="89"/>
       <c r="E67" s="46"/>
-      <c r="F67" s="93"/>
+      <c r="F67" s="65"/>
       <c r="G67" s="47"/>
       <c r="H67" s="47"/>
       <c r="I67" s="47"/>
       <c r="J67" s="47"/>
       <c r="K67" s="47"/>
     </row>
-    <row r="68" spans="1:19" s="33" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" s="33" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A68" s="29" t="s">
         <v>0</v>
       </c>
@@ -2538,10 +2538,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A69" s="15"/>
-      <c r="B69" s="77"/>
-      <c r="C69" s="78"/>
+      <c r="B69" s="52"/>
+      <c r="C69" s="53"/>
       <c r="D69" s="24" t="s">
         <v>16</v>
       </c>
@@ -2557,14 +2557,14 @@
       </c>
       <c r="K69" s="28"/>
     </row>
-    <row r="70" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="3">
         <v>48</v>
       </c>
-      <c r="B70" s="84"/>
-      <c r="C70" s="85"/>
-      <c r="D70" s="86"/>
-      <c r="E70" s="86"/>
+      <c r="B70" s="57"/>
+      <c r="C70" s="58"/>
+      <c r="D70" s="59"/>
+      <c r="E70" s="59"/>
       <c r="F70" s="18"/>
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
@@ -2580,15 +2580,15 @@
       <c r="R70" s="4"/>
       <c r="S70" s="21"/>
     </row>
-    <row r="71" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="3">
         <v>49</v>
       </c>
-      <c r="B71" s="84"/>
-      <c r="C71" s="85"/>
-      <c r="D71" s="86"/>
-      <c r="E71" s="86"/>
-      <c r="F71" s="86"/>
+      <c r="B71" s="57"/>
+      <c r="C71" s="58"/>
+      <c r="D71" s="59"/>
+      <c r="E71" s="59"/>
+      <c r="F71" s="59"/>
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
       <c r="I71" s="2"/>
@@ -2603,15 +2603,15 @@
       <c r="R71" s="4"/>
       <c r="S71" s="21"/>
     </row>
-    <row r="72" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="3">
         <v>50</v>
       </c>
-      <c r="B72" s="84"/>
-      <c r="C72" s="85"/>
-      <c r="D72" s="86"/>
-      <c r="E72" s="86"/>
-      <c r="F72" s="86"/>
+      <c r="B72" s="57"/>
+      <c r="C72" s="58"/>
+      <c r="D72" s="59"/>
+      <c r="E72" s="59"/>
+      <c r="F72" s="59"/>
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
       <c r="I72" s="2"/>
@@ -2626,15 +2626,15 @@
       <c r="R72" s="4"/>
       <c r="S72" s="21"/>
     </row>
-    <row r="73" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="3">
         <v>51</v>
       </c>
-      <c r="B73" s="84"/>
-      <c r="C73" s="85"/>
-      <c r="D73" s="86"/>
-      <c r="E73" s="86"/>
-      <c r="F73" s="86"/>
+      <c r="B73" s="57"/>
+      <c r="C73" s="58"/>
+      <c r="D73" s="59"/>
+      <c r="E73" s="59"/>
+      <c r="F73" s="59"/>
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
       <c r="I73" s="2"/>
@@ -2649,15 +2649,15 @@
       <c r="R73" s="4"/>
       <c r="S73" s="21"/>
     </row>
-    <row r="74" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="3">
         <v>52</v>
       </c>
-      <c r="B74" s="84"/>
-      <c r="C74" s="85"/>
-      <c r="D74" s="86"/>
-      <c r="E74" s="86"/>
-      <c r="F74" s="86"/>
+      <c r="B74" s="57"/>
+      <c r="C74" s="58"/>
+      <c r="D74" s="59"/>
+      <c r="E74" s="59"/>
+      <c r="F74" s="59"/>
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
       <c r="I74" s="2"/>
@@ -2672,15 +2672,15 @@
       <c r="R74" s="4"/>
       <c r="S74" s="21"/>
     </row>
-    <row r="75" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="3">
         <v>53</v>
       </c>
-      <c r="B75" s="84"/>
-      <c r="C75" s="85"/>
-      <c r="D75" s="86"/>
-      <c r="E75" s="86"/>
-      <c r="F75" s="86"/>
+      <c r="B75" s="57"/>
+      <c r="C75" s="58"/>
+      <c r="D75" s="59"/>
+      <c r="E75" s="59"/>
+      <c r="F75" s="59"/>
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
       <c r="I75" s="2"/>
@@ -2695,15 +2695,15 @@
       <c r="R75" s="4"/>
       <c r="S75" s="21"/>
     </row>
-    <row r="76" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="3">
         <v>54</v>
       </c>
-      <c r="B76" s="84"/>
-      <c r="C76" s="85"/>
-      <c r="D76" s="86"/>
-      <c r="E76" s="86"/>
-      <c r="F76" s="86"/>
+      <c r="B76" s="57"/>
+      <c r="C76" s="58"/>
+      <c r="D76" s="59"/>
+      <c r="E76" s="59"/>
+      <c r="F76" s="59"/>
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
       <c r="I76" s="2"/>
@@ -2718,15 +2718,15 @@
       <c r="R76" s="4"/>
       <c r="S76" s="21"/>
     </row>
-    <row r="77" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="3">
         <v>55</v>
       </c>
-      <c r="B77" s="86"/>
-      <c r="C77" s="86"/>
-      <c r="D77" s="86"/>
-      <c r="E77" s="86"/>
-      <c r="F77" s="86"/>
+      <c r="B77" s="59"/>
+      <c r="C77" s="59"/>
+      <c r="D77" s="59"/>
+      <c r="E77" s="59"/>
+      <c r="F77" s="59"/>
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
       <c r="I77" s="2"/>
@@ -2741,15 +2741,15 @@
       <c r="R77" s="4"/>
       <c r="S77" s="21"/>
     </row>
-    <row r="78" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="3">
         <v>56</v>
       </c>
-      <c r="B78" s="86"/>
-      <c r="C78" s="86"/>
-      <c r="D78" s="86"/>
-      <c r="E78" s="86"/>
-      <c r="F78" s="86"/>
+      <c r="B78" s="59"/>
+      <c r="C78" s="59"/>
+      <c r="D78" s="59"/>
+      <c r="E78" s="59"/>
+      <c r="F78" s="59"/>
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
       <c r="I78" s="2"/>
@@ -2764,15 +2764,15 @@
       <c r="R78" s="4"/>
       <c r="S78" s="21"/>
     </row>
-    <row r="79" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="3">
         <v>57</v>
       </c>
-      <c r="B79" s="86"/>
-      <c r="C79" s="86"/>
-      <c r="D79" s="86"/>
-      <c r="E79" s="86"/>
-      <c r="F79" s="86"/>
+      <c r="B79" s="59"/>
+      <c r="C79" s="59"/>
+      <c r="D79" s="59"/>
+      <c r="E79" s="59"/>
+      <c r="F79" s="59"/>
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
       <c r="I79" s="2"/>
@@ -2787,15 +2787,15 @@
       <c r="R79" s="4"/>
       <c r="S79" s="21"/>
     </row>
-    <row r="80" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="3">
         <v>58</v>
       </c>
-      <c r="B80" s="86"/>
-      <c r="C80" s="86"/>
-      <c r="D80" s="86"/>
-      <c r="E80" s="86"/>
-      <c r="F80" s="86"/>
+      <c r="B80" s="59"/>
+      <c r="C80" s="59"/>
+      <c r="D80" s="59"/>
+      <c r="E80" s="59"/>
+      <c r="F80" s="59"/>
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
       <c r="I80" s="2"/>
@@ -2810,15 +2810,15 @@
       <c r="R80" s="4"/>
       <c r="S80" s="21"/>
     </row>
-    <row r="81" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="3">
         <v>59</v>
       </c>
-      <c r="B81" s="86"/>
-      <c r="C81" s="86"/>
-      <c r="D81" s="86"/>
-      <c r="E81" s="86"/>
-      <c r="F81" s="86"/>
+      <c r="B81" s="59"/>
+      <c r="C81" s="59"/>
+      <c r="D81" s="59"/>
+      <c r="E81" s="59"/>
+      <c r="F81" s="59"/>
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
       <c r="I81" s="2"/>
@@ -2833,15 +2833,15 @@
       <c r="R81" s="4"/>
       <c r="S81" s="21"/>
     </row>
-    <row r="82" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="3">
         <v>60</v>
       </c>
-      <c r="B82" s="86"/>
-      <c r="C82" s="86"/>
-      <c r="D82" s="86"/>
-      <c r="E82" s="86"/>
-      <c r="F82" s="86"/>
+      <c r="B82" s="59"/>
+      <c r="C82" s="59"/>
+      <c r="D82" s="59"/>
+      <c r="E82" s="59"/>
+      <c r="F82" s="59"/>
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
       <c r="I82" s="2"/>
@@ -2856,15 +2856,15 @@
       <c r="R82" s="4"/>
       <c r="S82" s="21"/>
     </row>
-    <row r="83" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="3">
         <v>61</v>
       </c>
-      <c r="B83" s="86"/>
-      <c r="C83" s="86"/>
-      <c r="D83" s="86"/>
-      <c r="E83" s="86"/>
-      <c r="F83" s="86"/>
+      <c r="B83" s="59"/>
+      <c r="C83" s="59"/>
+      <c r="D83" s="59"/>
+      <c r="E83" s="59"/>
+      <c r="F83" s="59"/>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
       <c r="I83" s="2"/>
@@ -2879,15 +2879,15 @@
       <c r="R83" s="4"/>
       <c r="S83" s="21"/>
     </row>
-    <row r="84" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="3">
         <v>62</v>
       </c>
-      <c r="B84" s="86"/>
-      <c r="C84" s="86"/>
-      <c r="D84" s="86"/>
-      <c r="E84" s="86"/>
-      <c r="F84" s="86"/>
+      <c r="B84" s="59"/>
+      <c r="C84" s="59"/>
+      <c r="D84" s="59"/>
+      <c r="E84" s="59"/>
+      <c r="F84" s="59"/>
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
       <c r="I84" s="2"/>
@@ -2902,15 +2902,15 @@
       <c r="R84" s="4"/>
       <c r="S84" s="21"/>
     </row>
-    <row r="85" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="3">
         <v>63</v>
       </c>
-      <c r="B85" s="86"/>
-      <c r="C85" s="86"/>
-      <c r="D85" s="86"/>
-      <c r="E85" s="86"/>
-      <c r="F85" s="86"/>
+      <c r="B85" s="59"/>
+      <c r="C85" s="59"/>
+      <c r="D85" s="59"/>
+      <c r="E85" s="59"/>
+      <c r="F85" s="59"/>
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
       <c r="I85" s="2"/>
@@ -2925,15 +2925,15 @@
       <c r="R85" s="4"/>
       <c r="S85" s="21"/>
     </row>
-    <row r="86" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:19" s="16" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="3">
         <v>64</v>
       </c>
-      <c r="B86" s="86"/>
-      <c r="C86" s="86"/>
-      <c r="D86" s="86"/>
-      <c r="E86" s="86"/>
-      <c r="F86" s="86"/>
+      <c r="B86" s="59"/>
+      <c r="C86" s="59"/>
+      <c r="D86" s="59"/>
+      <c r="E86" s="59"/>
+      <c r="F86" s="59"/>
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
       <c r="I86" s="2"/>
@@ -2948,54 +2948,38 @@
       <c r="R86" s="4"/>
       <c r="S86" s="21"/>
     </row>
-    <row r="87" spans="1:19" s="23" customFormat="1" ht="70.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:19" s="23" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="36"/>
-      <c r="B87" s="50" t="s">
+      <c r="B87" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="C87" s="50"/>
-      <c r="D87" s="50"/>
+      <c r="C87" s="75"/>
+      <c r="D87" s="75"/>
       <c r="E87" s="39"/>
-      <c r="F87" s="90"/>
+      <c r="F87" s="63"/>
       <c r="G87" s="4"/>
       <c r="H87" s="4"/>
       <c r="I87" s="4"/>
       <c r="J87" s="4"/>
       <c r="K87" s="4"/>
     </row>
-    <row r="88" spans="1:19" s="45" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B88" s="51" t="s">
+    <row r="88" spans="1:19" s="45" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B88" s="89" t="s">
         <v>18</v>
       </c>
-      <c r="C88" s="51"/>
-      <c r="D88" s="51"/>
+      <c r="C88" s="89"/>
+      <c r="D88" s="89"/>
       <c r="E88" s="46"/>
-      <c r="F88" s="93"/>
+      <c r="F88" s="65"/>
       <c r="G88" s="47"/>
       <c r="H88" s="47"/>
       <c r="I88" s="47"/>
       <c r="J88" s="47"/>
       <c r="K88" s="47"/>
     </row>
-    <row r="89" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:K1"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="D4:G4"/>
-    <mergeCell ref="A4:C6"/>
-    <mergeCell ref="K7:K8"/>
     <mergeCell ref="B66:D66"/>
     <mergeCell ref="B67:D67"/>
     <mergeCell ref="B87:D87"/>
@@ -3012,6 +2996,22 @@
     <mergeCell ref="D13:F13"/>
     <mergeCell ref="D14:F14"/>
     <mergeCell ref="B9:C9"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:K1"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D4:G4"/>
+    <mergeCell ref="A4:C6"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B11:C11"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
